--- a/backend/data/financials_by_company/1997.HK.xlsx
+++ b/backend/data/financials_by_company/1997.HK.xlsx
@@ -4459,7 +4459,7 @@
         <v>6768000000</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
         <v>0.7829900400000001</v>
